--- a/Documents/HardwareCheckList_V43 3 1.xlsx
+++ b/Documents/HardwareCheckList_V43 3 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Qx_HW_CheckList\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\KiCad\Project_2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE94BB9-7AD4-48E0-8D76-5A08E74853F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CE1C1B-0DE3-46EC-831A-D0E38B177B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirments" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="266">
   <si>
     <t>QUANTTRONIX HARDWARE CHECKLIST</t>
   </si>
@@ -856,6 +856,9 @@
   </si>
   <si>
     <t>7ot parallel w wahed tany in series</t>
+  </si>
+  <si>
+    <t>Applied 3la el I2C</t>
   </si>
 </sst>
 </file>
@@ -1302,54 +1305,6 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="10" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1368,6 +1323,54 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -1855,19 +1858,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="81"/>
+      <c r="B1" s="88"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="82"/>
+      <c r="B2" s="89"/>
       <c r="C2" s="4"/>
     </row>
     <row r="3" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
@@ -1902,32 +1905,32 @@
     <col min="4" max="4" width="164" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.85546875" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" style="56" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="101.7109375" style="96" customWidth="1"/>
+    <col min="7" max="7" width="101.7109375" style="80" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -1947,7 +1950,7 @@
       <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="76" t="s">
+      <c r="A4" s="83" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="41">
@@ -1963,15 +1966,15 @@
         <v>10</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="G4" s="81" t="s">
         <v>225</v>
       </c>
       <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="41">
         <v>2</v>
       </c>
@@ -1983,13 +1986,13 @@
         <v>10</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G5" s="75"/>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="76"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="41">
         <v>3</v>
       </c>
@@ -2001,14 +2004,14 @@
         <v>10</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="76" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="76"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="41">
         <v>4</v>
       </c>
@@ -2020,15 +2023,15 @@
         <v>10</v>
       </c>
       <c r="F7" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="75" t="s">
         <v>227</v>
       </c>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="76"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="41">
         <v>5</v>
       </c>
@@ -2040,15 +2043,15 @@
         <v>10</v>
       </c>
       <c r="F8" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="75" t="s">
         <v>228</v>
       </c>
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="76"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="41">
         <v>6</v>
       </c>
@@ -2058,15 +2061,15 @@
       </c>
       <c r="E9" s="50"/>
       <c r="F9" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="75" t="s">
         <v>229</v>
       </c>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="41">
         <v>7</v>
       </c>
@@ -2078,15 +2081,15 @@
         <v>10</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="75" t="s">
         <v>230</v>
       </c>
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="76"/>
+      <c r="A11" s="83"/>
       <c r="B11" s="41">
         <v>8</v>
       </c>
@@ -2098,15 +2101,15 @@
         <v>10</v>
       </c>
       <c r="F11" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G11" s="75" t="s">
         <v>231</v>
       </c>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="76"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="41">
         <v>9</v>
       </c>
@@ -2118,15 +2121,15 @@
         <v>10</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="77" t="s">
         <v>232</v>
       </c>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="76"/>
+      <c r="A13" s="83"/>
       <c r="B13" s="41">
         <v>10</v>
       </c>
@@ -2138,15 +2141,15 @@
         <v>10</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G13" s="75" t="s">
         <v>233</v>
       </c>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="76"/>
+      <c r="A14" s="83"/>
       <c r="B14" s="41">
         <v>11</v>
       </c>
@@ -2158,15 +2161,15 @@
         <v>10</v>
       </c>
       <c r="F14" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G14" s="75" t="s">
         <v>233</v>
       </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
+      <c r="A15" s="83"/>
       <c r="B15" s="41">
         <v>12</v>
       </c>
@@ -2178,15 +2181,15 @@
         <v>10</v>
       </c>
       <c r="F15" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G15" s="75" t="s">
         <v>234</v>
       </c>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="41">
         <v>13</v>
       </c>
@@ -2198,15 +2201,15 @@
         <v>10</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G16" s="75" t="s">
         <v>235</v>
       </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="76"/>
+      <c r="A17" s="83"/>
       <c r="B17" s="41">
         <v>14</v>
       </c>
@@ -2218,14 +2221,14 @@
         <v>10</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="G17" s="76" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
+      <c r="A18" s="83"/>
       <c r="B18" s="41">
         <v>15</v>
       </c>
@@ -2237,15 +2240,15 @@
         <v>10</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="G18" s="77" t="s">
         <v>237</v>
       </c>
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="41">
         <v>16</v>
       </c>
@@ -2257,15 +2260,15 @@
         <v>10</v>
       </c>
       <c r="F19" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="93" t="s">
+        <v>222</v>
+      </c>
+      <c r="G19" s="77" t="s">
         <v>238</v>
       </c>
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="41">
         <v>17</v>
       </c>
@@ -2277,15 +2280,15 @@
         <v>10</v>
       </c>
       <c r="F20" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="93" t="s">
+        <v>222</v>
+      </c>
+      <c r="G20" s="77" t="s">
         <v>239</v>
       </c>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="84" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="42">
@@ -2299,14 +2302,14 @@
         <v>10</v>
       </c>
       <c r="F21" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="G21" s="76" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="77"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="42">
         <v>19</v>
       </c>
@@ -2318,15 +2321,15 @@
         <v>31</v>
       </c>
       <c r="F22" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22" s="91">
+        <v>223</v>
+      </c>
+      <c r="G22" s="75">
         <v>2.54</v>
       </c>
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="77"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="42">
         <v>20</v>
       </c>
@@ -2338,15 +2341,15 @@
         <v>10</v>
       </c>
       <c r="F23" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G23" s="75" t="s">
         <v>241</v>
       </c>
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="77"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="42">
         <v>21</v>
       </c>
@@ -2358,15 +2361,15 @@
         <v>10</v>
       </c>
       <c r="F24" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="96" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="80" t="s">
         <v>243</v>
       </c>
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="77"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="42">
         <v>22</v>
       </c>
@@ -2378,14 +2381,14 @@
         <v>10</v>
       </c>
       <c r="F25" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="75" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="77"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="42">
         <v>23</v>
       </c>
@@ -2397,15 +2400,15 @@
         <v>10</v>
       </c>
       <c r="F26" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="75" t="s">
         <v>244</v>
       </c>
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="77"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="42">
         <v>24</v>
       </c>
@@ -2417,13 +2420,15 @@
         <v>10</v>
       </c>
       <c r="F27" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G27" s="75" t="s">
+        <v>265</v>
+      </c>
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="77"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="42">
         <v>25</v>
       </c>
@@ -2435,15 +2440,15 @@
         <v>38</v>
       </c>
       <c r="F28" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G28" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="75" t="s">
         <v>245</v>
       </c>
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="42">
         <v>26</v>
       </c>
@@ -2455,15 +2460,15 @@
         <v>38</v>
       </c>
       <c r="F29" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G29" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G29" s="75" t="s">
         <v>246</v>
       </c>
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="77"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="42">
         <v>27</v>
       </c>
@@ -2475,15 +2480,15 @@
         <v>38</v>
       </c>
       <c r="F30" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="G30" s="80" t="s">
         <v>247</v>
       </c>
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="77"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="42">
         <v>28</v>
       </c>
@@ -2495,15 +2500,15 @@
         <v>38</v>
       </c>
       <c r="F31" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" s="75" t="s">
         <v>248</v>
       </c>
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="77"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="42">
         <v>29</v>
       </c>
@@ -2515,15 +2520,15 @@
         <v>38</v>
       </c>
       <c r="F32" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G32" s="75" t="s">
         <v>249</v>
       </c>
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="77"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="42">
         <v>30</v>
       </c>
@@ -2535,15 +2540,15 @@
         <v>38</v>
       </c>
       <c r="F33" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G33" s="75" t="s">
         <v>251</v>
       </c>
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="77"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="42">
         <v>31</v>
       </c>
@@ -2555,15 +2560,15 @@
         <v>38</v>
       </c>
       <c r="F34" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G34" s="75" t="s">
         <v>252</v>
       </c>
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="77"/>
+      <c r="A35" s="84"/>
       <c r="B35" s="42">
         <v>32</v>
       </c>
@@ -2575,15 +2580,15 @@
         <v>38</v>
       </c>
       <c r="F35" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G35" s="75" t="s">
         <v>253</v>
       </c>
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="77"/>
+      <c r="A36" s="84"/>
       <c r="B36" s="42">
         <v>33</v>
       </c>
@@ -2595,13 +2600,13 @@
         <v>38</v>
       </c>
       <c r="F36" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G36" s="75"/>
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
+      <c r="A37" s="84"/>
       <c r="B37" s="42">
         <v>34</v>
       </c>
@@ -2613,12 +2618,12 @@
         <v>38</v>
       </c>
       <c r="F37" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="92"/>
+        <v>222</v>
+      </c>
+      <c r="G37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="77"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="42">
         <v>35</v>
       </c>
@@ -2630,13 +2635,13 @@
         <v>38</v>
       </c>
       <c r="F38" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G38" s="75"/>
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
+      <c r="A39" s="84"/>
       <c r="B39" s="42">
         <v>36</v>
       </c>
@@ -2648,14 +2653,14 @@
         <v>50</v>
       </c>
       <c r="F39" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="92" t="s">
+        <v>222</v>
+      </c>
+      <c r="G39" s="76" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="77"/>
+      <c r="A40" s="84"/>
       <c r="B40" s="42">
         <v>37</v>
       </c>
@@ -2667,13 +2672,13 @@
         <v>10</v>
       </c>
       <c r="F40" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G40" s="75"/>
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="77"/>
+      <c r="A41" s="84"/>
       <c r="B41" s="42">
         <v>38</v>
       </c>
@@ -2685,15 +2690,15 @@
         <v>10</v>
       </c>
       <c r="F41" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G41" s="75" t="s">
         <v>254</v>
       </c>
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="77"/>
+      <c r="A42" s="84"/>
       <c r="B42" s="42">
         <v>39</v>
       </c>
@@ -2707,13 +2712,13 @@
       <c r="F42" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="91" t="s">
+      <c r="G42" s="75" t="s">
         <v>255</v>
       </c>
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="77"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="42">
         <v>40</v>
       </c>
@@ -2725,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="F43" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G43" s="75"/>
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="77"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="42">
         <v>41</v>
       </c>
@@ -2743,13 +2748,13 @@
         <v>10</v>
       </c>
       <c r="F44" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G44" s="75"/>
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="77"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="42">
         <v>42</v>
       </c>
@@ -2761,15 +2766,15 @@
         <v>10</v>
       </c>
       <c r="F45" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G45" s="75" t="s">
         <v>256</v>
       </c>
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="77"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="42">
         <v>43</v>
       </c>
@@ -2783,13 +2788,13 @@
         <v>10</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G46" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G46" s="75"/>
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="80" t="s">
+      <c r="A47" s="87" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="43">
@@ -2803,15 +2808,15 @@
         <v>10</v>
       </c>
       <c r="F47" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G47" s="75"/>
       <c r="H47" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="80"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="43">
         <v>45</v>
       </c>
@@ -2823,13 +2828,13 @@
         <v>10</v>
       </c>
       <c r="F48" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G48" s="75"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="80"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="43">
         <v>46</v>
       </c>
@@ -2841,15 +2846,15 @@
         <v>10</v>
       </c>
       <c r="F49" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" s="75" t="s">
         <v>257</v>
       </c>
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="80"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="43">
         <v>47</v>
       </c>
@@ -2861,13 +2866,13 @@
         <v>10</v>
       </c>
       <c r="F50" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G50" s="75"/>
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="80"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="43">
         <v>48</v>
       </c>
@@ -2879,12 +2884,12 @@
         <v>10</v>
       </c>
       <c r="F51" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="94"/>
+        <v>223</v>
+      </c>
+      <c r="G51" s="78"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="83" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="41">
@@ -2902,11 +2907,11 @@
       <c r="F52" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G52" s="91"/>
+      <c r="G52" s="75"/>
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="76"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="41">
         <v>50</v>
       </c>
@@ -2918,14 +2923,14 @@
         <v>10</v>
       </c>
       <c r="F53" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53" s="92" t="s">
+        <v>223</v>
+      </c>
+      <c r="G53" s="76" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="76"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="41">
         <v>51</v>
       </c>
@@ -2937,13 +2942,13 @@
         <v>10</v>
       </c>
       <c r="F54" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G54" s="75"/>
       <c r="H54" s="8"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="76"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="41">
         <v>52</v>
       </c>
@@ -2955,15 +2960,15 @@
         <v>10</v>
       </c>
       <c r="F55" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55" s="91" t="s">
+        <v>224</v>
+      </c>
+      <c r="G55" s="75" t="s">
         <v>259</v>
       </c>
       <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="76"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="41">
         <v>53</v>
       </c>
@@ -2975,13 +2980,13 @@
         <v>10</v>
       </c>
       <c r="F56" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G56" s="75"/>
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="76"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="41">
         <v>54</v>
       </c>
@@ -2993,15 +2998,15 @@
         <v>10</v>
       </c>
       <c r="F57" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G57" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G57" s="75" t="s">
         <v>260</v>
       </c>
       <c r="H57" s="8"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="76"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="41">
         <v>55</v>
       </c>
@@ -3013,13 +3018,13 @@
         <v>10</v>
       </c>
       <c r="F58" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="91"/>
+        <v>224</v>
+      </c>
+      <c r="G58" s="75"/>
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="76"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="41">
         <v>56</v>
       </c>
@@ -3031,13 +3036,13 @@
         <v>10</v>
       </c>
       <c r="F59" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G59" s="75"/>
       <c r="H59" s="8"/>
     </row>
     <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="76"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="41">
         <v>57</v>
       </c>
@@ -3051,11 +3056,11 @@
       <c r="F60" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G60" s="91"/>
+      <c r="G60" s="75"/>
       <c r="H60" s="8"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="76"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="41">
         <v>58</v>
       </c>
@@ -3069,11 +3074,11 @@
       <c r="F61" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G61" s="91"/>
+      <c r="G61" s="75"/>
       <c r="H61" s="8"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="76"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="41">
         <v>59</v>
       </c>
@@ -3085,13 +3090,13 @@
         <v>261</v>
       </c>
       <c r="F62" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G62" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G62" s="75"/>
       <c r="H62" s="8"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="77" t="s">
+      <c r="A63" s="84" t="s">
         <v>78</v>
       </c>
       <c r="B63" s="42">
@@ -3105,13 +3110,13 @@
         <v>10</v>
       </c>
       <c r="F63" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G63" s="91"/>
+        <v>222</v>
+      </c>
+      <c r="G63" s="75"/>
       <c r="H63" s="8"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="77"/>
+      <c r="A64" s="84"/>
       <c r="B64" s="42">
         <v>61</v>
       </c>
@@ -3123,15 +3128,15 @@
         <v>10</v>
       </c>
       <c r="F64" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64" s="91" t="s">
+        <v>223</v>
+      </c>
+      <c r="G64" s="75" t="s">
         <v>262</v>
       </c>
       <c r="H64" s="8"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="77"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="42">
         <v>62</v>
       </c>
@@ -3143,13 +3148,13 @@
         <v>10</v>
       </c>
       <c r="F65" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G65" s="75"/>
       <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="77"/>
+      <c r="A66" s="84"/>
       <c r="B66" s="42">
         <v>63</v>
       </c>
@@ -3161,13 +3166,13 @@
         <v>10</v>
       </c>
       <c r="F66" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G66" s="75"/>
       <c r="H66" s="8"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="77"/>
+      <c r="A67" s="84"/>
       <c r="B67" s="42">
         <v>64</v>
       </c>
@@ -3179,15 +3184,15 @@
         <v>10</v>
       </c>
       <c r="F67" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G67" s="91" t="s">
+        <v>222</v>
+      </c>
+      <c r="G67" s="75" t="s">
         <v>263</v>
       </c>
       <c r="H67" s="8"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="77"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="42">
         <v>65</v>
       </c>
@@ -3201,11 +3206,11 @@
       <c r="F68" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G68" s="91"/>
+      <c r="G68" s="75"/>
       <c r="H68" s="8"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="77"/>
+      <c r="A69" s="84"/>
       <c r="B69" s="42">
         <v>66</v>
       </c>
@@ -3217,13 +3222,13 @@
         <v>10</v>
       </c>
       <c r="F69" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="91"/>
+        <v>224</v>
+      </c>
+      <c r="G69" s="75"/>
       <c r="H69" s="8"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="77"/>
+      <c r="A70" s="84"/>
       <c r="B70" s="42">
         <v>67</v>
       </c>
@@ -3237,11 +3242,11 @@
       <c r="F70" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="91"/>
+      <c r="G70" s="75"/>
       <c r="H70" s="8"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="77"/>
+      <c r="A71" s="84"/>
       <c r="B71" s="42">
         <v>68</v>
       </c>
@@ -3255,10 +3260,10 @@
       <c r="F71" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="92"/>
+      <c r="G71" s="76"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="77"/>
+      <c r="A72" s="84"/>
       <c r="B72" s="42">
         <v>69</v>
       </c>
@@ -3272,11 +3277,11 @@
       <c r="F72" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G72" s="91"/>
+      <c r="G72" s="75"/>
       <c r="H72" s="8"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="77"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="42">
         <v>70</v>
       </c>
@@ -3290,11 +3295,11 @@
       <c r="F73" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G73" s="91"/>
+      <c r="G73" s="75"/>
       <c r="H73" s="8"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="77"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="42">
         <v>71</v>
       </c>
@@ -3308,11 +3313,11 @@
       <c r="F74" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G74" s="91"/>
+      <c r="G74" s="75"/>
       <c r="H74" s="8"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="77"/>
+      <c r="A75" s="84"/>
       <c r="B75" s="42">
         <v>72</v>
       </c>
@@ -3326,11 +3331,11 @@
       <c r="F75" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G75" s="91"/>
+      <c r="G75" s="75"/>
       <c r="H75" s="8"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="77"/>
+      <c r="A76" s="84"/>
       <c r="B76" s="42">
         <v>73</v>
       </c>
@@ -3344,11 +3349,11 @@
       <c r="F76" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G76" s="91"/>
+      <c r="G76" s="75"/>
       <c r="H76" s="8"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="77"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="42">
         <v>74</v>
       </c>
@@ -3362,11 +3367,11 @@
       <c r="F77" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G77" s="91"/>
+      <c r="G77" s="75"/>
       <c r="H77" s="8"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="77"/>
+      <c r="A78" s="84"/>
       <c r="B78" s="42">
         <v>75</v>
       </c>
@@ -3380,13 +3385,13 @@
       <c r="F78" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G78" s="91" t="s">
+      <c r="G78" s="75" t="s">
         <v>264</v>
       </c>
       <c r="H78" s="8"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="75" t="s">
+      <c r="A79" s="82" t="s">
         <v>96</v>
       </c>
       <c r="B79" s="43">
@@ -3400,13 +3405,13 @@
         <v>98</v>
       </c>
       <c r="F79" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G79" s="91"/>
+        <v>223</v>
+      </c>
+      <c r="G79" s="75"/>
       <c r="H79" s="8"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="75"/>
+      <c r="A80" s="82"/>
       <c r="B80" s="43">
         <v>77</v>
       </c>
@@ -3420,11 +3425,11 @@
       <c r="F80" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G80" s="91"/>
+      <c r="G80" s="75"/>
       <c r="H80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="75"/>
+      <c r="A81" s="82"/>
       <c r="B81" s="43">
         <v>78</v>
       </c>
@@ -3440,10 +3445,10 @@
       <c r="F81" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G81" s="95"/>
+      <c r="G81" s="79"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="75"/>
+      <c r="A82" s="82"/>
       <c r="B82" s="43">
         <v>79</v>
       </c>
@@ -3457,10 +3462,10 @@
       <c r="F82" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G82" s="95"/>
+      <c r="G82" s="79"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="75"/>
+      <c r="A83" s="82"/>
       <c r="B83" s="43">
         <v>80</v>
       </c>
@@ -3474,7 +3479,7 @@
       <c r="F83" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G83" s="92"/>
+      <c r="G83" s="76"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D84" s="4"/>
@@ -3612,26 +3617,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="94" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
-      <c r="G2" s="87"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35"/>
@@ -3649,7 +3654,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="84" t="s">
+      <c r="A4" s="91" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="62">
@@ -3670,7 +3675,7 @@
       <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
+      <c r="A5" s="91"/>
       <c r="B5" s="62">
         <v>2</v>
       </c>
@@ -3687,7 +3692,7 @@
       <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="84"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="62">
         <v>3</v>
       </c>
@@ -3704,7 +3709,7 @@
       <c r="G6" s="23"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="84"/>
+      <c r="A7" s="91"/>
       <c r="B7" s="62">
         <v>4</v>
       </c>
@@ -3721,7 +3726,7 @@
       <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="84"/>
+      <c r="A8" s="91"/>
       <c r="B8" s="62">
         <v>5</v>
       </c>
@@ -3738,7 +3743,7 @@
       <c r="G8" s="23"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="84"/>
+      <c r="A9" s="91"/>
       <c r="B9" s="62">
         <v>6</v>
       </c>
@@ -3755,7 +3760,7 @@
       <c r="G9" s="23"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="84"/>
+      <c r="A10" s="91"/>
       <c r="B10" s="62">
         <v>7</v>
       </c>
@@ -3772,7 +3777,7 @@
       <c r="G10" s="23"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="88" t="s">
+      <c r="A11" s="95" t="s">
         <v>115</v>
       </c>
       <c r="B11" s="66">
@@ -3791,7 +3796,7 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="88"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="66">
         <v>9</v>
       </c>
@@ -3808,7 +3813,7 @@
       <c r="G12" s="23"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="88"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="66">
         <v>10</v>
       </c>
@@ -3825,7 +3830,7 @@
       <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="88"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="66">
         <v>11</v>
       </c>
@@ -3842,7 +3847,7 @@
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="88"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="66">
         <v>12</v>
       </c>
@@ -3859,7 +3864,7 @@
       <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="88"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="66">
         <v>13</v>
       </c>
@@ -3876,7 +3881,7 @@
       <c r="G16" s="23"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="88"/>
+      <c r="A17" s="95"/>
       <c r="B17" s="66">
         <v>14</v>
       </c>
@@ -3893,7 +3898,7 @@
       <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="88"/>
+      <c r="A18" s="95"/>
       <c r="B18" s="66">
         <v>15</v>
       </c>
@@ -3910,7 +3915,7 @@
       <c r="G18" s="23"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
+      <c r="A19" s="95"/>
       <c r="B19" s="66">
         <v>16</v>
       </c>
@@ -3927,7 +3932,7 @@
       <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="88"/>
+      <c r="A20" s="95"/>
       <c r="B20" s="66">
         <v>17</v>
       </c>
@@ -3944,7 +3949,7 @@
       <c r="G20" s="23"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="88"/>
+      <c r="A21" s="95"/>
       <c r="B21" s="66">
         <v>18</v>
       </c>
@@ -3961,7 +3966,7 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="92" t="s">
         <v>128</v>
       </c>
       <c r="B22" s="72">
@@ -3980,7 +3985,7 @@
       <c r="G22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="85"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="72">
         <v>20</v>
       </c>
@@ -3997,7 +4002,7 @@
       <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="85"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="72">
         <v>21</v>
       </c>
@@ -4014,7 +4019,7 @@
       <c r="G24" s="23"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="85"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="72">
         <v>22</v>
       </c>
@@ -4031,7 +4036,7 @@
       <c r="G25" s="23"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="85"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="72">
         <v>23</v>
       </c>
@@ -4048,7 +4053,7 @@
       <c r="G26" s="23"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="85"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="72">
         <v>24</v>
       </c>
@@ -4065,7 +4070,7 @@
       <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="85"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="72">
         <v>25</v>
       </c>
@@ -4082,7 +4087,7 @@
       <c r="G28" s="23"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="85"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="72">
         <v>26</v>
       </c>
@@ -4099,7 +4104,7 @@
       <c r="G29" s="23"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="91" t="s">
         <v>137</v>
       </c>
       <c r="B30" s="62">
@@ -4118,7 +4123,7 @@
       <c r="G30" s="23"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="91"/>
       <c r="B31" s="62">
         <v>28</v>
       </c>
@@ -4135,7 +4140,7 @@
       <c r="G31" s="23"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
+      <c r="A32" s="91"/>
       <c r="B32" s="62">
         <v>29</v>
       </c>
@@ -4152,7 +4157,7 @@
       <c r="G32" s="23"/>
     </row>
     <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
+      <c r="A33" s="91"/>
       <c r="B33" s="62">
         <v>30</v>
       </c>
@@ -4169,7 +4174,7 @@
       <c r="G33" s="23"/>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
+      <c r="A34" s="91"/>
       <c r="B34" s="62">
         <v>31</v>
       </c>
@@ -4186,7 +4191,7 @@
       <c r="G34" s="23"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="84"/>
+      <c r="A35" s="91"/>
       <c r="B35" s="62">
         <v>32</v>
       </c>
@@ -4203,7 +4208,7 @@
       <c r="G35" s="23"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="84"/>
+      <c r="A36" s="91"/>
       <c r="B36" s="62">
         <v>33</v>
       </c>
@@ -4220,7 +4225,7 @@
       <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="84"/>
+      <c r="A37" s="91"/>
       <c r="B37" s="62">
         <v>34</v>
       </c>
@@ -4237,7 +4242,7 @@
       <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="84"/>
+      <c r="A38" s="91"/>
       <c r="B38" s="62">
         <v>35</v>
       </c>
@@ -4254,7 +4259,7 @@
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="84"/>
+      <c r="A39" s="91"/>
       <c r="B39" s="62">
         <v>36</v>
       </c>
@@ -4271,7 +4276,7 @@
       <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="84"/>
+      <c r="A40" s="91"/>
       <c r="B40" s="62">
         <v>37</v>
       </c>
@@ -4288,7 +4293,7 @@
       <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="84"/>
+      <c r="A41" s="91"/>
       <c r="B41" s="62">
         <v>38</v>
       </c>
@@ -4305,7 +4310,7 @@
       <c r="G41" s="23"/>
     </row>
     <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="84"/>
+      <c r="A42" s="91"/>
       <c r="B42" s="62">
         <v>39</v>
       </c>
@@ -4322,7 +4327,7 @@
       <c r="G42" s="23"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="84"/>
+      <c r="A43" s="91"/>
       <c r="B43" s="62">
         <v>40</v>
       </c>
@@ -4339,7 +4344,7 @@
       <c r="G43" s="23"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
+      <c r="A44" s="91"/>
       <c r="B44" s="62">
         <v>41</v>
       </c>
@@ -4356,7 +4361,7 @@
       <c r="G44" s="23"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="84"/>
+      <c r="A45" s="91"/>
       <c r="B45" s="62">
         <v>42</v>
       </c>
@@ -4373,7 +4378,7 @@
       <c r="G45" s="23"/>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="84"/>
+      <c r="A46" s="91"/>
       <c r="B46" s="62">
         <v>43</v>
       </c>
@@ -4390,7 +4395,7 @@
       <c r="G46" s="23"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="88" t="s">
+      <c r="A47" s="95" t="s">
         <v>157</v>
       </c>
       <c r="B47" s="66">
@@ -4409,7 +4414,7 @@
       <c r="G47" s="23"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="88"/>
+      <c r="A48" s="95"/>
       <c r="B48" s="66">
         <v>45</v>
       </c>
@@ -4426,7 +4431,7 @@
       <c r="G48" s="23"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="88"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="66">
         <v>46</v>
       </c>
@@ -4443,7 +4448,7 @@
       <c r="G49" s="23"/>
     </row>
     <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="88"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="66">
         <v>47</v>
       </c>
@@ -4460,7 +4465,7 @@
       <c r="G50" s="23"/>
     </row>
     <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="66">
         <v>48</v>
       </c>
@@ -4477,7 +4482,7 @@
       <c r="G51" s="23"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="88"/>
+      <c r="A52" s="95"/>
       <c r="B52" s="66">
         <v>49</v>
       </c>
@@ -4494,7 +4499,7 @@
       <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="88"/>
+      <c r="A53" s="95"/>
       <c r="B53" s="66">
         <v>50</v>
       </c>
@@ -4511,7 +4516,7 @@
       <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="88"/>
+      <c r="A54" s="95"/>
       <c r="B54" s="66">
         <v>51</v>
       </c>
@@ -4528,7 +4533,7 @@
       <c r="G54" s="23"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="88"/>
+      <c r="A55" s="95"/>
       <c r="B55" s="66">
         <v>52</v>
       </c>
@@ -4545,7 +4550,7 @@
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="88"/>
+      <c r="A56" s="95"/>
       <c r="B56" s="66">
         <v>53</v>
       </c>
@@ -4562,7 +4567,7 @@
       <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="88"/>
+      <c r="A57" s="95"/>
       <c r="B57" s="66">
         <v>54</v>
       </c>
@@ -4579,7 +4584,7 @@
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="88"/>
+      <c r="A58" s="95"/>
       <c r="B58" s="66">
         <v>55</v>
       </c>
@@ -4596,7 +4601,7 @@
       <c r="G58" s="23"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="88"/>
+      <c r="A59" s="95"/>
       <c r="B59" s="66">
         <v>56</v>
       </c>
@@ -4613,7 +4618,7 @@
       <c r="G59" s="23"/>
     </row>
     <row r="60" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A60" s="88"/>
+      <c r="A60" s="95"/>
       <c r="B60" s="66">
         <v>57</v>
       </c>
@@ -4630,7 +4635,7 @@
       <c r="G60" s="23"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="88"/>
+      <c r="A61" s="95"/>
       <c r="B61" s="66">
         <v>58</v>
       </c>
@@ -4647,7 +4652,7 @@
       <c r="G61" s="23"/>
     </row>
     <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="88"/>
+      <c r="A62" s="95"/>
       <c r="B62" s="66">
         <v>59</v>
       </c>
@@ -4664,7 +4669,7 @@
       <c r="G62" s="23"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="88"/>
+      <c r="A63" s="95"/>
       <c r="B63" s="66">
         <v>60</v>
       </c>
@@ -4681,7 +4686,7 @@
       <c r="G63" s="23"/>
     </row>
     <row r="64" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="88"/>
+      <c r="A64" s="95"/>
       <c r="B64" s="66">
         <v>61</v>
       </c>
@@ -4698,7 +4703,7 @@
       <c r="G64" s="23"/>
     </row>
     <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="88"/>
+      <c r="A65" s="95"/>
       <c r="B65" s="66">
         <v>62</v>
       </c>
@@ -4715,7 +4720,7 @@
       <c r="G65" s="23"/>
     </row>
     <row r="66" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="88"/>
+      <c r="A66" s="95"/>
       <c r="B66" s="66">
         <v>63</v>
       </c>
@@ -4732,7 +4737,7 @@
       <c r="G66" s="23"/>
     </row>
     <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="88"/>
+      <c r="A67" s="95"/>
       <c r="B67" s="66">
         <v>64</v>
       </c>
@@ -4749,7 +4754,7 @@
       <c r="G67" s="23"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="88"/>
+      <c r="A68" s="95"/>
       <c r="B68" s="66">
         <v>65</v>
       </c>
@@ -4766,7 +4771,7 @@
       <c r="G68" s="23"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="88"/>
+      <c r="A69" s="95"/>
       <c r="B69" s="66">
         <v>66</v>
       </c>
@@ -4783,7 +4788,7 @@
       <c r="G69" s="23"/>
     </row>
     <row r="70" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A70" s="88"/>
+      <c r="A70" s="95"/>
       <c r="B70" s="66">
         <v>67</v>
       </c>
@@ -4800,7 +4805,7 @@
       <c r="G70" s="23"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="85" t="s">
+      <c r="A71" s="92" t="s">
         <v>189</v>
       </c>
       <c r="B71" s="72">
@@ -4819,7 +4824,7 @@
       <c r="G71" s="23"/>
     </row>
     <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="85"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="72">
         <v>69</v>
       </c>
@@ -4836,7 +4841,7 @@
       <c r="G72" s="23"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="85"/>
+      <c r="A73" s="92"/>
       <c r="B73" s="72">
         <v>70</v>
       </c>
@@ -4853,7 +4858,7 @@
       <c r="G73" s="23"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="85"/>
+      <c r="A74" s="92"/>
       <c r="B74" s="72">
         <v>71</v>
       </c>
@@ -4870,7 +4875,7 @@
       <c r="G74" s="23"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="85"/>
+      <c r="A75" s="92"/>
       <c r="B75" s="72">
         <v>72</v>
       </c>
@@ -4887,7 +4892,7 @@
       <c r="G75" s="23"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="83" t="s">
+      <c r="A76" s="90" t="s">
         <v>196</v>
       </c>
       <c r="B76" s="62">
@@ -4906,7 +4911,7 @@
       <c r="G76" s="23"/>
     </row>
     <row r="77" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="84"/>
+      <c r="A77" s="91"/>
       <c r="B77" s="62">
         <v>74</v>
       </c>
@@ -5046,20 +5051,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
     </row>
     <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="97" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
     </row>
     <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>

--- a/Documents/HardwareCheckList_V43 3 1.xlsx
+++ b/Documents/HardwareCheckList_V43 3 1.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\KiCad\Project_2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CE1C1B-0DE3-46EC-831A-D0E38B177B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E3FCE9-C54E-4A07-9410-D383AE0D437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="2" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="3" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirments" sheetId="5" r:id="rId1"/>
     <sheet name="Schematic Checklist" sheetId="4" r:id="rId2"/>
-    <sheet name="PCB Checklist" sheetId="2" r:id="rId3"/>
-    <sheet name="Production Files Checklist" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId3"/>
+    <sheet name="PCB Checklist" sheetId="2" r:id="rId4"/>
+    <sheet name="Production Files Checklist" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Schematic Checklist'!$D$3:$D$83</definedName>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">Sheet1!$A$1:$A$5</definedName>
+    <definedName name="ExternalData_1" localSheetId="5" hidden="1">Sheet1!$A$1:$A$5</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="273">
   <si>
     <t>QUANTTRONIX HARDWARE CHECKLIST</t>
   </si>
@@ -859,13 +860,34 @@
   </si>
   <si>
     <t>Applied 3la el I2C</t>
+  </si>
+  <si>
+    <t>Components Used</t>
+  </si>
+  <si>
+    <t>Component No.</t>
+  </si>
+  <si>
+    <t>Part No.</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>23mlha wla eh</t>
+  </si>
+  <si>
+    <t>Not all of them</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -992,8 +1014,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1057,6 +1092,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1095,7 +1136,7 @@
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1324,6 +1365,30 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1342,35 +1407,17 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="10" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -1910,27 +1957,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -1950,7 +1997,7 @@
       <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="91" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="41">
@@ -1974,7 +2021,7 @@
       <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="83"/>
+      <c r="A5" s="91"/>
       <c r="B5" s="41">
         <v>2</v>
       </c>
@@ -1992,7 +2039,7 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="41">
         <v>3</v>
       </c>
@@ -2011,7 +2058,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
+      <c r="A7" s="91"/>
       <c r="B7" s="41">
         <v>4</v>
       </c>
@@ -2031,7 +2078,7 @@
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
+      <c r="A8" s="91"/>
       <c r="B8" s="41">
         <v>5</v>
       </c>
@@ -2051,7 +2098,7 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
+      <c r="A9" s="91"/>
       <c r="B9" s="41">
         <v>6</v>
       </c>
@@ -2069,7 +2116,7 @@
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
+      <c r="A10" s="91"/>
       <c r="B10" s="41">
         <v>7</v>
       </c>
@@ -2089,7 +2136,7 @@
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="83"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="41">
         <v>8</v>
       </c>
@@ -2109,7 +2156,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="83"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="41">
         <v>9</v>
       </c>
@@ -2129,7 +2176,7 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="83"/>
+      <c r="A13" s="91"/>
       <c r="B13" s="41">
         <v>10</v>
       </c>
@@ -2149,7 +2196,7 @@
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="83"/>
+      <c r="A14" s="91"/>
       <c r="B14" s="41">
         <v>11</v>
       </c>
@@ -2169,7 +2216,7 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="83"/>
+      <c r="A15" s="91"/>
       <c r="B15" s="41">
         <v>12</v>
       </c>
@@ -2189,7 +2236,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="83"/>
+      <c r="A16" s="91"/>
       <c r="B16" s="41">
         <v>13</v>
       </c>
@@ -2209,7 +2256,7 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
+      <c r="A17" s="91"/>
       <c r="B17" s="41">
         <v>14</v>
       </c>
@@ -2228,7 +2275,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="83"/>
+      <c r="A18" s="91"/>
       <c r="B18" s="41">
         <v>15</v>
       </c>
@@ -2248,7 +2295,7 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="83"/>
+      <c r="A19" s="91"/>
       <c r="B19" s="41">
         <v>16</v>
       </c>
@@ -2268,7 +2315,7 @@
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="83"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="41">
         <v>17</v>
       </c>
@@ -2288,7 +2335,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="92" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="42">
@@ -2309,7 +2356,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="84"/>
+      <c r="A22" s="92"/>
       <c r="B22" s="42">
         <v>19</v>
       </c>
@@ -2329,7 +2376,7 @@
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="42">
         <v>20</v>
       </c>
@@ -2349,7 +2396,7 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="42">
         <v>21</v>
       </c>
@@ -2369,7 +2416,7 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="42">
         <v>22</v>
       </c>
@@ -2388,7 +2435,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="42">
         <v>23</v>
       </c>
@@ -2408,7 +2455,7 @@
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="42">
         <v>24</v>
       </c>
@@ -2428,7 +2475,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="42">
         <v>25</v>
       </c>
@@ -2448,7 +2495,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="42">
         <v>26</v>
       </c>
@@ -2468,7 +2515,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="84"/>
+      <c r="A30" s="92"/>
       <c r="B30" s="42">
         <v>27</v>
       </c>
@@ -2488,7 +2535,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="84"/>
+      <c r="A31" s="92"/>
       <c r="B31" s="42">
         <v>28</v>
       </c>
@@ -2508,7 +2555,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="84"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="42">
         <v>29</v>
       </c>
@@ -2528,7 +2575,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="84"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="42">
         <v>30</v>
       </c>
@@ -2548,7 +2595,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="84"/>
+      <c r="A34" s="92"/>
       <c r="B34" s="42">
         <v>31</v>
       </c>
@@ -2568,7 +2615,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="84"/>
+      <c r="A35" s="92"/>
       <c r="B35" s="42">
         <v>32</v>
       </c>
@@ -2588,7 +2635,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="84"/>
+      <c r="A36" s="92"/>
       <c r="B36" s="42">
         <v>33</v>
       </c>
@@ -2606,7 +2653,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="84"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="42">
         <v>34</v>
       </c>
@@ -2623,7 +2670,7 @@
       <c r="G37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="84"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="42">
         <v>35</v>
       </c>
@@ -2641,7 +2688,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="84"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="42">
         <v>36</v>
       </c>
@@ -2660,7 +2707,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="84"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="42">
         <v>37</v>
       </c>
@@ -2678,7 +2725,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="84"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="42">
         <v>38</v>
       </c>
@@ -2698,7 +2745,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="84"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="42">
         <v>39</v>
       </c>
@@ -2718,7 +2765,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="84"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="42">
         <v>40</v>
       </c>
@@ -2736,7 +2783,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="84"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="42">
         <v>41</v>
       </c>
@@ -2754,7 +2801,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="84"/>
+      <c r="A45" s="92"/>
       <c r="B45" s="42">
         <v>42</v>
       </c>
@@ -2774,7 +2821,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="84"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="42">
         <v>43</v>
       </c>
@@ -2794,7 +2841,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="95" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="43">
@@ -2816,7 +2863,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
+      <c r="A48" s="95"/>
       <c r="B48" s="43">
         <v>45</v>
       </c>
@@ -2834,7 +2881,7 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="43">
         <v>46</v>
       </c>
@@ -2854,7 +2901,7 @@
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="43">
         <v>47</v>
       </c>
@@ -2872,7 +2919,7 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="87"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="43">
         <v>48</v>
       </c>
@@ -2889,7 +2936,7 @@
       <c r="G51" s="78"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="83" t="s">
+      <c r="A52" s="91" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="41">
@@ -2911,7 +2958,7 @@
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="83"/>
+      <c r="A53" s="91"/>
       <c r="B53" s="41">
         <v>50</v>
       </c>
@@ -2930,7 +2977,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="83"/>
+      <c r="A54" s="91"/>
       <c r="B54" s="41">
         <v>51</v>
       </c>
@@ -2948,7 +2995,7 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="83"/>
+      <c r="A55" s="91"/>
       <c r="B55" s="41">
         <v>52</v>
       </c>
@@ -2968,7 +3015,7 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="83"/>
+      <c r="A56" s="91"/>
       <c r="B56" s="41">
         <v>53</v>
       </c>
@@ -2986,7 +3033,7 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="83"/>
+      <c r="A57" s="91"/>
       <c r="B57" s="41">
         <v>54</v>
       </c>
@@ -3006,7 +3053,7 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="83"/>
+      <c r="A58" s="91"/>
       <c r="B58" s="41">
         <v>55</v>
       </c>
@@ -3024,7 +3071,7 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="83"/>
+      <c r="A59" s="91"/>
       <c r="B59" s="41">
         <v>56</v>
       </c>
@@ -3042,7 +3089,7 @@
       <c r="H59" s="8"/>
     </row>
     <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="83"/>
+      <c r="A60" s="91"/>
       <c r="B60" s="41">
         <v>57</v>
       </c>
@@ -3060,7 +3107,7 @@
       <c r="H60" s="8"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="83"/>
+      <c r="A61" s="91"/>
       <c r="B61" s="41">
         <v>58</v>
       </c>
@@ -3078,7 +3125,7 @@
       <c r="H61" s="8"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="83"/>
+      <c r="A62" s="91"/>
       <c r="B62" s="41">
         <v>59</v>
       </c>
@@ -3096,7 +3143,7 @@
       <c r="H62" s="8"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="84" t="s">
+      <c r="A63" s="92" t="s">
         <v>78</v>
       </c>
       <c r="B63" s="42">
@@ -3116,7 +3163,7 @@
       <c r="H63" s="8"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="84"/>
+      <c r="A64" s="92"/>
       <c r="B64" s="42">
         <v>61</v>
       </c>
@@ -3136,7 +3183,7 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="84"/>
+      <c r="A65" s="92"/>
       <c r="B65" s="42">
         <v>62</v>
       </c>
@@ -3154,7 +3201,7 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="84"/>
+      <c r="A66" s="92"/>
       <c r="B66" s="42">
         <v>63</v>
       </c>
@@ -3172,7 +3219,7 @@
       <c r="H66" s="8"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="84"/>
+      <c r="A67" s="92"/>
       <c r="B67" s="42">
         <v>64</v>
       </c>
@@ -3192,7 +3239,7 @@
       <c r="H67" s="8"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="84"/>
+      <c r="A68" s="92"/>
       <c r="B68" s="42">
         <v>65</v>
       </c>
@@ -3210,7 +3257,7 @@
       <c r="H68" s="8"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="84"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="42">
         <v>66</v>
       </c>
@@ -3228,7 +3275,7 @@
       <c r="H69" s="8"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="84"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="42">
         <v>67</v>
       </c>
@@ -3246,7 +3293,7 @@
       <c r="H70" s="8"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="84"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="42">
         <v>68</v>
       </c>
@@ -3260,10 +3307,12 @@
       <c r="F71" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G71" s="76"/>
+      <c r="G71" s="76" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="84"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="42">
         <v>69</v>
       </c>
@@ -3275,13 +3324,13 @@
         <v>10</v>
       </c>
       <c r="F72" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G72" s="75"/>
       <c r="H72" s="8"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="84"/>
+      <c r="A73" s="92"/>
       <c r="B73" s="42">
         <v>70</v>
       </c>
@@ -3293,13 +3342,13 @@
         <v>10</v>
       </c>
       <c r="F73" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G73" s="75"/>
       <c r="H73" s="8"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="84"/>
+      <c r="A74" s="92"/>
       <c r="B74" s="42">
         <v>71</v>
       </c>
@@ -3311,13 +3360,13 @@
         <v>10</v>
       </c>
       <c r="F74" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G74" s="75"/>
       <c r="H74" s="8"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="84"/>
+      <c r="A75" s="92"/>
       <c r="B75" s="42">
         <v>72</v>
       </c>
@@ -3329,13 +3378,13 @@
         <v>10</v>
       </c>
       <c r="F75" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G75" s="75"/>
       <c r="H75" s="8"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="84"/>
+      <c r="A76" s="92"/>
       <c r="B76" s="42">
         <v>73</v>
       </c>
@@ -3347,13 +3396,13 @@
         <v>93</v>
       </c>
       <c r="F76" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G76" s="75"/>
       <c r="H76" s="8"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="84"/>
+      <c r="A77" s="92"/>
       <c r="B77" s="42">
         <v>74</v>
       </c>
@@ -3365,13 +3414,13 @@
         <v>10</v>
       </c>
       <c r="F77" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G77" s="75"/>
       <c r="H77" s="8"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="84"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="42">
         <v>75</v>
       </c>
@@ -3383,7 +3432,7 @@
         <v>10</v>
       </c>
       <c r="F78" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G78" s="75" t="s">
         <v>264</v>
@@ -3391,7 +3440,7 @@
       <c r="H78" s="8"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="82" t="s">
+      <c r="A79" s="90" t="s">
         <v>96</v>
       </c>
       <c r="B79" s="43">
@@ -3411,7 +3460,7 @@
       <c r="H79" s="8"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="82"/>
+      <c r="A80" s="90"/>
       <c r="B80" s="43">
         <v>77</v>
       </c>
@@ -3423,13 +3472,13 @@
         <v>98</v>
       </c>
       <c r="F80" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G80" s="75"/>
       <c r="H80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="82"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="43">
         <v>78</v>
       </c>
@@ -3443,12 +3492,12 @@
         <v>98</v>
       </c>
       <c r="F81" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G81" s="79"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="82"/>
+      <c r="A82" s="90"/>
       <c r="B82" s="43">
         <v>79</v>
       </c>
@@ -3460,12 +3509,12 @@
         <v>102</v>
       </c>
       <c r="F82" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G82" s="79"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="82"/>
+      <c r="A83" s="90"/>
       <c r="B83" s="43">
         <v>80</v>
       </c>
@@ -3603,6 +3652,179 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC47803-8EEB-4FC5-8290-9A07B139AC2E}">
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
+    <col min="3" max="3" width="106.7109375" customWidth="1"/>
+    <col min="4" max="4" width="66.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="98" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="99"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="99"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="99"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="99"/>
+      <c r="I3" s="99"/>
+      <c r="J3" s="99"/>
+      <c r="K3" s="99"/>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="99"/>
+      <c r="O3" s="99"/>
+      <c r="P3" s="99"/>
+      <c r="Q3" s="99"/>
+      <c r="R3" s="99"/>
+      <c r="S3" s="99"/>
+      <c r="T3" s="99"/>
+      <c r="U3" s="99"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="99"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="99"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="99"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="99"/>
+      <c r="Q6" s="99"/>
+      <c r="R6" s="99"/>
+      <c r="S6" s="99"/>
+      <c r="T6" s="99"/>
+      <c r="U6" s="99"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84B04926-C3FF-4FC4-9C00-E803CA16E1B6}">
   <dimension ref="A1:G83"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
@@ -3617,26 +3839,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="86" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35"/>
@@ -3654,7 +3876,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="83" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="62">
@@ -3670,12 +3892,12 @@
         <v>10</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="91"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="62">
         <v>2</v>
       </c>
@@ -3687,12 +3909,12 @@
         <v>109</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="91"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="62">
         <v>3</v>
       </c>
@@ -3704,12 +3926,12 @@
         <v>10</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G6" s="23"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="91"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="62">
         <v>4</v>
       </c>
@@ -3721,12 +3943,12 @@
         <v>10</v>
       </c>
       <c r="F7" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="62">
         <v>5</v>
       </c>
@@ -3738,12 +3960,12 @@
         <v>10</v>
       </c>
       <c r="F8" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G8" s="23"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="62">
         <v>6</v>
       </c>
@@ -3755,12 +3977,12 @@
         <v>10</v>
       </c>
       <c r="F9" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G9" s="23"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="62">
         <v>7</v>
       </c>
@@ -3772,12 +3994,12 @@
         <v>10</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G10" s="23"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="87" t="s">
         <v>115</v>
       </c>
       <c r="B11" s="66">
@@ -3791,12 +4013,12 @@
         <v>109</v>
       </c>
       <c r="F11" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="95"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="66">
         <v>9</v>
       </c>
@@ -3808,12 +4030,12 @@
         <v>10</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G12" s="23"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="95"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="66">
         <v>10</v>
       </c>
@@ -3830,7 +4052,7 @@
       <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="95"/>
+      <c r="A14" s="87"/>
       <c r="B14" s="66">
         <v>11</v>
       </c>
@@ -3842,12 +4064,12 @@
         <v>10</v>
       </c>
       <c r="F14" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="95"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="66">
         <v>12</v>
       </c>
@@ -3859,12 +4081,12 @@
         <v>121</v>
       </c>
       <c r="F15" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="95"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="66">
         <v>13</v>
       </c>
@@ -3876,12 +4098,12 @@
         <v>10</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G16" s="23"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="95"/>
+      <c r="A17" s="87"/>
       <c r="B17" s="66">
         <v>14</v>
       </c>
@@ -3893,12 +4115,12 @@
         <v>10</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="95"/>
+      <c r="A18" s="87"/>
       <c r="B18" s="66">
         <v>15</v>
       </c>
@@ -3910,12 +4132,14 @@
         <v>10</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="23"/>
+        <v>224</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="95"/>
+      <c r="A19" s="87"/>
       <c r="B19" s="66">
         <v>16</v>
       </c>
@@ -3927,12 +4151,12 @@
         <v>10</v>
       </c>
       <c r="F19" s="61" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="95"/>
+      <c r="A20" s="87"/>
       <c r="B20" s="66">
         <v>17</v>
       </c>
@@ -3949,7 +4173,7 @@
       <c r="G20" s="23"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="95"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="66">
         <v>18</v>
       </c>
@@ -3966,7 +4190,7 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="84" t="s">
         <v>128</v>
       </c>
       <c r="B22" s="72">
@@ -3985,7 +4209,7 @@
       <c r="G22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="72">
         <v>20</v>
       </c>
@@ -4002,7 +4226,7 @@
       <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="92"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="72">
         <v>21</v>
       </c>
@@ -4019,7 +4243,7 @@
       <c r="G24" s="23"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="72">
         <v>22</v>
       </c>
@@ -4036,7 +4260,7 @@
       <c r="G25" s="23"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="92"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="72">
         <v>23</v>
       </c>
@@ -4053,7 +4277,7 @@
       <c r="G26" s="23"/>
     </row>
     <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="72">
         <v>24</v>
       </c>
@@ -4070,7 +4294,7 @@
       <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="92"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="72">
         <v>25</v>
       </c>
@@ -4082,12 +4306,12 @@
         <v>10</v>
       </c>
       <c r="F28" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G28" s="23"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="92"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="72">
         <v>26</v>
       </c>
@@ -4104,7 +4328,7 @@
       <c r="G29" s="23"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="91" t="s">
+      <c r="A30" s="83" t="s">
         <v>137</v>
       </c>
       <c r="B30" s="62">
@@ -4123,7 +4347,7 @@
       <c r="G30" s="23"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="91"/>
+      <c r="A31" s="83"/>
       <c r="B31" s="62">
         <v>28</v>
       </c>
@@ -4140,7 +4364,7 @@
       <c r="G31" s="23"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="91"/>
+      <c r="A32" s="83"/>
       <c r="B32" s="62">
         <v>29</v>
       </c>
@@ -4157,7 +4381,7 @@
       <c r="G32" s="23"/>
     </row>
     <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="91"/>
+      <c r="A33" s="83"/>
       <c r="B33" s="62">
         <v>30</v>
       </c>
@@ -4174,7 +4398,7 @@
       <c r="G33" s="23"/>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="91"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="62">
         <v>31</v>
       </c>
@@ -4191,7 +4415,7 @@
       <c r="G34" s="23"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="91"/>
+      <c r="A35" s="83"/>
       <c r="B35" s="62">
         <v>32</v>
       </c>
@@ -4208,7 +4432,7 @@
       <c r="G35" s="23"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="91"/>
+      <c r="A36" s="83"/>
       <c r="B36" s="62">
         <v>33</v>
       </c>
@@ -4225,7 +4449,7 @@
       <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="91"/>
+      <c r="A37" s="83"/>
       <c r="B37" s="62">
         <v>34</v>
       </c>
@@ -4242,7 +4466,7 @@
       <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="91"/>
+      <c r="A38" s="83"/>
       <c r="B38" s="62">
         <v>35</v>
       </c>
@@ -4259,7 +4483,7 @@
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
+      <c r="A39" s="83"/>
       <c r="B39" s="62">
         <v>36</v>
       </c>
@@ -4276,7 +4500,7 @@
       <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="91"/>
+      <c r="A40" s="83"/>
       <c r="B40" s="62">
         <v>37</v>
       </c>
@@ -4293,7 +4517,7 @@
       <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="91"/>
+      <c r="A41" s="83"/>
       <c r="B41" s="62">
         <v>38</v>
       </c>
@@ -4310,7 +4534,7 @@
       <c r="G41" s="23"/>
     </row>
     <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="91"/>
+      <c r="A42" s="83"/>
       <c r="B42" s="62">
         <v>39</v>
       </c>
@@ -4327,7 +4551,7 @@
       <c r="G42" s="23"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="91"/>
+      <c r="A43" s="83"/>
       <c r="B43" s="62">
         <v>40</v>
       </c>
@@ -4344,7 +4568,7 @@
       <c r="G43" s="23"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="91"/>
+      <c r="A44" s="83"/>
       <c r="B44" s="62">
         <v>41</v>
       </c>
@@ -4361,7 +4585,7 @@
       <c r="G44" s="23"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="91"/>
+      <c r="A45" s="83"/>
       <c r="B45" s="62">
         <v>42</v>
       </c>
@@ -4378,7 +4602,7 @@
       <c r="G45" s="23"/>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="91"/>
+      <c r="A46" s="83"/>
       <c r="B46" s="62">
         <v>43</v>
       </c>
@@ -4395,7 +4619,7 @@
       <c r="G46" s="23"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="95" t="s">
+      <c r="A47" s="87" t="s">
         <v>157</v>
       </c>
       <c r="B47" s="66">
@@ -4414,7 +4638,7 @@
       <c r="G47" s="23"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="95"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="66">
         <v>45</v>
       </c>
@@ -4431,7 +4655,7 @@
       <c r="G48" s="23"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="95"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="66">
         <v>46</v>
       </c>
@@ -4448,7 +4672,7 @@
       <c r="G49" s="23"/>
     </row>
     <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="95"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="66">
         <v>47</v>
       </c>
@@ -4465,7 +4689,7 @@
       <c r="G50" s="23"/>
     </row>
     <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="95"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="66">
         <v>48</v>
       </c>
@@ -4482,7 +4706,7 @@
       <c r="G51" s="23"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="95"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="66">
         <v>49</v>
       </c>
@@ -4499,7 +4723,7 @@
       <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="95"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="66">
         <v>50</v>
       </c>
@@ -4516,7 +4740,7 @@
       <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="95"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="66">
         <v>51</v>
       </c>
@@ -4533,7 +4757,7 @@
       <c r="G54" s="23"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="95"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="66">
         <v>52</v>
       </c>
@@ -4550,7 +4774,7 @@
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="95"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="66">
         <v>53</v>
       </c>
@@ -4567,7 +4791,7 @@
       <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="95"/>
+      <c r="A57" s="87"/>
       <c r="B57" s="66">
         <v>54</v>
       </c>
@@ -4584,7 +4808,7 @@
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="95"/>
+      <c r="A58" s="87"/>
       <c r="B58" s="66">
         <v>55</v>
       </c>
@@ -4601,7 +4825,7 @@
       <c r="G58" s="23"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="95"/>
+      <c r="A59" s="87"/>
       <c r="B59" s="66">
         <v>56</v>
       </c>
@@ -4618,7 +4842,7 @@
       <c r="G59" s="23"/>
     </row>
     <row r="60" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A60" s="95"/>
+      <c r="A60" s="87"/>
       <c r="B60" s="66">
         <v>57</v>
       </c>
@@ -4635,7 +4859,7 @@
       <c r="G60" s="23"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="95"/>
+      <c r="A61" s="87"/>
       <c r="B61" s="66">
         <v>58</v>
       </c>
@@ -4652,7 +4876,7 @@
       <c r="G61" s="23"/>
     </row>
     <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="95"/>
+      <c r="A62" s="87"/>
       <c r="B62" s="66">
         <v>59</v>
       </c>
@@ -4669,7 +4893,7 @@
       <c r="G62" s="23"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="95"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="66">
         <v>60</v>
       </c>
@@ -4686,7 +4910,7 @@
       <c r="G63" s="23"/>
     </row>
     <row r="64" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="95"/>
+      <c r="A64" s="87"/>
       <c r="B64" s="66">
         <v>61</v>
       </c>
@@ -4703,7 +4927,7 @@
       <c r="G64" s="23"/>
     </row>
     <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="95"/>
+      <c r="A65" s="87"/>
       <c r="B65" s="66">
         <v>62</v>
       </c>
@@ -4720,7 +4944,7 @@
       <c r="G65" s="23"/>
     </row>
     <row r="66" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="95"/>
+      <c r="A66" s="87"/>
       <c r="B66" s="66">
         <v>63</v>
       </c>
@@ -4737,7 +4961,7 @@
       <c r="G66" s="23"/>
     </row>
     <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="95"/>
+      <c r="A67" s="87"/>
       <c r="B67" s="66">
         <v>64</v>
       </c>
@@ -4754,7 +4978,7 @@
       <c r="G67" s="23"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="95"/>
+      <c r="A68" s="87"/>
       <c r="B68" s="66">
         <v>65</v>
       </c>
@@ -4771,7 +4995,7 @@
       <c r="G68" s="23"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="95"/>
+      <c r="A69" s="87"/>
       <c r="B69" s="66">
         <v>66</v>
       </c>
@@ -4788,7 +5012,7 @@
       <c r="G69" s="23"/>
     </row>
     <row r="70" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A70" s="95"/>
+      <c r="A70" s="87"/>
       <c r="B70" s="66">
         <v>67</v>
       </c>
@@ -4805,7 +5029,7 @@
       <c r="G70" s="23"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="92" t="s">
+      <c r="A71" s="84" t="s">
         <v>189</v>
       </c>
       <c r="B71" s="72">
@@ -4824,7 +5048,7 @@
       <c r="G71" s="23"/>
     </row>
     <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="92"/>
+      <c r="A72" s="84"/>
       <c r="B72" s="72">
         <v>69</v>
       </c>
@@ -4841,7 +5065,7 @@
       <c r="G72" s="23"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="92"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="72">
         <v>70</v>
       </c>
@@ -4858,7 +5082,7 @@
       <c r="G73" s="23"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="92"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="72">
         <v>71</v>
       </c>
@@ -4875,7 +5099,7 @@
       <c r="G74" s="23"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="92"/>
+      <c r="A75" s="84"/>
       <c r="B75" s="72">
         <v>72</v>
       </c>
@@ -4892,7 +5116,7 @@
       <c r="G75" s="23"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="90" t="s">
+      <c r="A76" s="82" t="s">
         <v>196</v>
       </c>
       <c r="B76" s="62">
@@ -4911,7 +5135,7 @@
       <c r="G76" s="23"/>
     </row>
     <row r="77" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="91"/>
+      <c r="A77" s="83"/>
       <c r="B77" s="62">
         <v>74</v>
       </c>
@@ -5040,7 +5264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E29A8A-79AE-4B9B-BCC2-2FD35D7E7A49}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5436,7 +5660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721096D2-81DC-4754-9403-3B97828ACEA7}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Documents/HardwareCheckList_V43 3 1.xlsx
+++ b/Documents/HardwareCheckList_V43 3 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\KiCad\Project_2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E3FCE9-C54E-4A07-9410-D383AE0D437C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044F690B-D4D4-428C-8AE6-E81828082756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="3" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
   </bookViews>
@@ -1407,17 +1407,17 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3663,144 +3663,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="96" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="99"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="97"/>
+      <c r="G2" s="97"/>
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="97"/>
+      <c r="U2" s="97"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="99"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="99"/>
-      <c r="U3" s="99"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-      <c r="U4" s="99"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="97"/>
+      <c r="P4" s="97"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="99"/>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="99"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="99"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="99"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="99"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="97"/>
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="97"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="99"/>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="99"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="99"/>
-      <c r="U6" s="99"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="97"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+      <c r="O6" s="97"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="97"/>
+      <c r="R6" s="97"/>
+      <c r="S6" s="97"/>
+      <c r="T6" s="97"/>
+      <c r="U6" s="97"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -3833,7 +3833,7 @@
     <col min="2" max="2" width="9.140625" style="16"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="118.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="53" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="53" customWidth="1"/>
     <col min="6" max="6" width="25.28515625" style="60" customWidth="1"/>
     <col min="7" max="7" width="36.85546875" customWidth="1"/>
   </cols>
@@ -4168,7 +4168,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G20" s="23"/>
     </row>
@@ -4185,7 +4185,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G21" s="23"/>
     </row>
@@ -4204,7 +4204,7 @@
         <v>10</v>
       </c>
       <c r="F22" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G22" s="23"/>
     </row>
@@ -4238,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="F24" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G24" s="23"/>
     </row>
@@ -4255,7 +4255,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G25" s="23"/>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="84"/>
       <c r="B27" s="72">
         <v>24</v>
@@ -4444,7 +4444,7 @@
         <v>10</v>
       </c>
       <c r="F36" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G36" s="23"/>
     </row>
@@ -4461,7 +4461,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G37" s="23"/>
     </row>
@@ -4478,7 +4478,7 @@
         <v>10</v>
       </c>
       <c r="F38" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G38" s="23"/>
     </row>
@@ -4495,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G39" s="23"/>
     </row>
@@ -4512,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="F40" s="61" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="G40" s="23"/>
     </row>
@@ -4529,7 +4529,7 @@
         <v>150</v>
       </c>
       <c r="F41" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G41" s="23"/>
     </row>
@@ -4546,7 +4546,7 @@
         <v>152</v>
       </c>
       <c r="F42" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G42" s="23"/>
     </row>
@@ -4563,7 +4563,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G43" s="23"/>
     </row>
@@ -4580,7 +4580,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G44" s="23"/>
     </row>
@@ -4597,7 +4597,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G45" s="23"/>
     </row>
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G47" s="23"/>
     </row>
@@ -4667,7 +4667,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G49" s="23"/>
     </row>
@@ -4684,7 +4684,7 @@
         <v>162</v>
       </c>
       <c r="F50" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G50" s="23"/>
     </row>
@@ -4701,7 +4701,7 @@
         <v>164</v>
       </c>
       <c r="F51" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G51" s="23"/>
     </row>
@@ -4718,7 +4718,7 @@
         <v>10</v>
       </c>
       <c r="F52" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G52" s="23"/>
     </row>
@@ -4735,7 +4735,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G53" s="23"/>
     </row>
@@ -4752,7 +4752,7 @@
         <v>10</v>
       </c>
       <c r="F54" s="61" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="G54" s="23"/>
     </row>
@@ -4769,7 +4769,7 @@
         <v>10</v>
       </c>
       <c r="F55" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G55" s="23"/>
     </row>
@@ -4786,7 +4786,7 @@
         <v>10</v>
       </c>
       <c r="F56" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G56" s="23"/>
     </row>
@@ -4803,7 +4803,7 @@
         <v>10</v>
       </c>
       <c r="F57" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G57" s="23"/>
     </row>
@@ -4837,7 +4837,7 @@
         <v>173</v>
       </c>
       <c r="F59" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G59" s="23"/>
     </row>
@@ -4871,7 +4871,7 @@
         <v>10</v>
       </c>
       <c r="F61" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G61" s="23"/>
     </row>
@@ -4888,7 +4888,7 @@
         <v>152</v>
       </c>
       <c r="F62" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G62" s="23"/>
     </row>
@@ -4905,7 +4905,7 @@
         <v>178</v>
       </c>
       <c r="F63" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G63" s="23"/>
     </row>
@@ -4922,7 +4922,7 @@
         <v>180</v>
       </c>
       <c r="F64" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G64" s="23"/>
     </row>
@@ -4939,7 +4939,7 @@
         <v>182</v>
       </c>
       <c r="F65" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G65" s="23"/>
     </row>
@@ -4973,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G67" s="23"/>
     </row>
@@ -4990,7 +4990,7 @@
         <v>10</v>
       </c>
       <c r="F68" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G68" s="23"/>
     </row>
@@ -5007,7 +5007,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G69" s="23"/>
     </row>
@@ -5043,7 +5043,7 @@
         <v>10</v>
       </c>
       <c r="F71" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G71" s="23"/>
     </row>
@@ -5060,7 +5060,7 @@
         <v>10</v>
       </c>
       <c r="F72" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G72" s="23"/>
     </row>
@@ -5077,7 +5077,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G73" s="23"/>
     </row>
@@ -5094,7 +5094,7 @@
         <v>194</v>
       </c>
       <c r="F74" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G74" s="23"/>
     </row>
@@ -5111,7 +5111,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G75" s="23"/>
     </row>
@@ -5130,7 +5130,7 @@
         <v>10</v>
       </c>
       <c r="F76" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G76" s="23"/>
     </row>
@@ -5147,7 +5147,7 @@
         <v>10</v>
       </c>
       <c r="F77" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G77" s="23"/>
     </row>
@@ -5275,20 +5275,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
     </row>
     <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="99" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
     </row>
     <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A3" s="26"/>

--- a/Documents/HardwareCheckList_V43 3 1.xlsx
+++ b/Documents/HardwareCheckList_V43 3 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\KiCad\Project_2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044F690B-D4D4-428C-8AE6-E81828082756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8126498-E4F8-4135-8214-D6DC0924CB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="3" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirments" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="274">
   <si>
     <t>QUANTTRONIX HARDWARE CHECKLIST</t>
   </si>
@@ -881,6 +881,9 @@
   </si>
   <si>
     <t>Not all of them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mt7otsh 2y haga without res connected to Vdd or </t>
   </si>
 </sst>
 </file>
@@ -3528,7 +3531,9 @@
       <c r="F83" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="G83" s="76"/>
+      <c r="G83" s="76" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D84" s="4"/>
@@ -4068,7 +4073,7 @@
       </c>
       <c r="G14" s="36"/>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="87"/>
       <c r="B15" s="66">
         <v>12</v>
@@ -4393,7 +4398,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G33" s="23"/>
     </row>
@@ -4533,7 +4538,7 @@
       </c>
       <c r="G41" s="23"/>
     </row>
-    <row r="42" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="83"/>
       <c r="B42" s="62">
         <v>39</v>

--- a/Documents/HardwareCheckList_V43 3 1.xlsx
+++ b/Documents/HardwareCheckList_V43 3 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\KiCad\Project_2\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8126498-E4F8-4135-8214-D6DC0924CB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2A765F-7B66-43AA-B7EE-4F56F2FCB5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="1" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="3" xr2:uid="{68843EE4-1B9F-4521-A53B-766934041111}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Requirments" sheetId="5" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="275">
   <si>
     <t>QUANTTRONIX HARDWARE CHECKLIST</t>
   </si>
@@ -884,6 +884,9 @@
   </si>
   <si>
     <t xml:space="preserve">mt7otsh 2y haga without res connected to Vdd or </t>
+  </si>
+  <si>
+    <t>y3ny tb2a t7ot mosfet w hagat mn kda</t>
   </si>
 </sst>
 </file>
@@ -1368,6 +1371,36 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1384,36 +1417,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1960,27 +1963,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
@@ -2000,7 +2003,7 @@
       <c r="H3" s="15"/>
     </row>
     <row r="4" spans="1:8" s="13" customFormat="1" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A4" s="91" t="s">
+      <c r="A4" s="83" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="41">
@@ -2024,7 +2027,7 @@
       <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="91"/>
+      <c r="A5" s="83"/>
       <c r="B5" s="41">
         <v>2</v>
       </c>
@@ -2042,7 +2045,7 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="91"/>
+      <c r="A6" s="83"/>
       <c r="B6" s="41">
         <v>3</v>
       </c>
@@ -2061,7 +2064,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="91"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="41">
         <v>4</v>
       </c>
@@ -2081,7 +2084,7 @@
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="91"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="41">
         <v>5</v>
       </c>
@@ -2101,7 +2104,7 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="91"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="41">
         <v>6</v>
       </c>
@@ -2119,7 +2122,7 @@
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="91"/>
+      <c r="A10" s="83"/>
       <c r="B10" s="41">
         <v>7</v>
       </c>
@@ -2139,7 +2142,7 @@
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="91"/>
+      <c r="A11" s="83"/>
       <c r="B11" s="41">
         <v>8</v>
       </c>
@@ -2159,7 +2162,7 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="91"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="41">
         <v>9</v>
       </c>
@@ -2179,7 +2182,7 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="91"/>
+      <c r="A13" s="83"/>
       <c r="B13" s="41">
         <v>10</v>
       </c>
@@ -2199,7 +2202,7 @@
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="91"/>
+      <c r="A14" s="83"/>
       <c r="B14" s="41">
         <v>11</v>
       </c>
@@ -2219,7 +2222,7 @@
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="91"/>
+      <c r="A15" s="83"/>
       <c r="B15" s="41">
         <v>12</v>
       </c>
@@ -2239,7 +2242,7 @@
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="91"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="41">
         <v>13</v>
       </c>
@@ -2259,7 +2262,7 @@
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
+      <c r="A17" s="83"/>
       <c r="B17" s="41">
         <v>14</v>
       </c>
@@ -2278,7 +2281,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="91"/>
+      <c r="A18" s="83"/>
       <c r="B18" s="41">
         <v>15</v>
       </c>
@@ -2298,7 +2301,7 @@
       <c r="H18" s="8"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="91"/>
+      <c r="A19" s="83"/>
       <c r="B19" s="41">
         <v>16</v>
       </c>
@@ -2318,7 +2321,7 @@
       <c r="H19" s="8"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="91"/>
+      <c r="A20" s="83"/>
       <c r="B20" s="41">
         <v>17</v>
       </c>
@@ -2338,7 +2341,7 @@
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="84" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="42">
@@ -2359,7 +2362,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="92"/>
+      <c r="A22" s="84"/>
       <c r="B22" s="42">
         <v>19</v>
       </c>
@@ -2379,7 +2382,7 @@
       <c r="H22" s="8"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="92"/>
+      <c r="A23" s="84"/>
       <c r="B23" s="42">
         <v>20</v>
       </c>
@@ -2399,7 +2402,7 @@
       <c r="H23" s="8"/>
     </row>
     <row r="24" spans="1:8" ht="37.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
+      <c r="A24" s="84"/>
       <c r="B24" s="42">
         <v>21</v>
       </c>
@@ -2419,7 +2422,7 @@
       <c r="H24" s="8"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="92"/>
+      <c r="A25" s="84"/>
       <c r="B25" s="42">
         <v>22</v>
       </c>
@@ -2438,7 +2441,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="92"/>
+      <c r="A26" s="84"/>
       <c r="B26" s="42">
         <v>23</v>
       </c>
@@ -2458,7 +2461,7 @@
       <c r="H26" s="8"/>
     </row>
     <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="92"/>
+      <c r="A27" s="84"/>
       <c r="B27" s="42">
         <v>24</v>
       </c>
@@ -2478,7 +2481,7 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="92"/>
+      <c r="A28" s="84"/>
       <c r="B28" s="42">
         <v>25</v>
       </c>
@@ -2498,7 +2501,7 @@
       <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="92"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="42">
         <v>26</v>
       </c>
@@ -2518,7 +2521,7 @@
       <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="92"/>
+      <c r="A30" s="84"/>
       <c r="B30" s="42">
         <v>27</v>
       </c>
@@ -2538,7 +2541,7 @@
       <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="92"/>
+      <c r="A31" s="84"/>
       <c r="B31" s="42">
         <v>28</v>
       </c>
@@ -2558,7 +2561,7 @@
       <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="92"/>
+      <c r="A32" s="84"/>
       <c r="B32" s="42">
         <v>29</v>
       </c>
@@ -2578,7 +2581,7 @@
       <c r="H32" s="8"/>
     </row>
     <row r="33" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="92"/>
+      <c r="A33" s="84"/>
       <c r="B33" s="42">
         <v>30</v>
       </c>
@@ -2598,7 +2601,7 @@
       <c r="H33" s="8"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="92"/>
+      <c r="A34" s="84"/>
       <c r="B34" s="42">
         <v>31</v>
       </c>
@@ -2618,7 +2621,7 @@
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="92"/>
+      <c r="A35" s="84"/>
       <c r="B35" s="42">
         <v>32</v>
       </c>
@@ -2638,7 +2641,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="92"/>
+      <c r="A36" s="84"/>
       <c r="B36" s="42">
         <v>33</v>
       </c>
@@ -2656,7 +2659,7 @@
       <c r="H36" s="8"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
+      <c r="A37" s="84"/>
       <c r="B37" s="42">
         <v>34</v>
       </c>
@@ -2673,7 +2676,7 @@
       <c r="G37" s="76"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="92"/>
+      <c r="A38" s="84"/>
       <c r="B38" s="42">
         <v>35</v>
       </c>
@@ -2691,7 +2694,7 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+      <c r="A39" s="84"/>
       <c r="B39" s="42">
         <v>36</v>
       </c>
@@ -2710,7 +2713,7 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="92"/>
+      <c r="A40" s="84"/>
       <c r="B40" s="42">
         <v>37</v>
       </c>
@@ -2728,7 +2731,7 @@
       <c r="H40" s="8"/>
     </row>
     <row r="41" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="92"/>
+      <c r="A41" s="84"/>
       <c r="B41" s="42">
         <v>38</v>
       </c>
@@ -2748,7 +2751,7 @@
       <c r="H41" s="8"/>
     </row>
     <row r="42" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="92"/>
+      <c r="A42" s="84"/>
       <c r="B42" s="42">
         <v>39</v>
       </c>
@@ -2768,7 +2771,7 @@
       <c r="H42" s="8"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="92"/>
+      <c r="A43" s="84"/>
       <c r="B43" s="42">
         <v>40</v>
       </c>
@@ -2786,7 +2789,7 @@
       <c r="H43" s="8"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="92"/>
+      <c r="A44" s="84"/>
       <c r="B44" s="42">
         <v>41</v>
       </c>
@@ -2804,7 +2807,7 @@
       <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="92"/>
+      <c r="A45" s="84"/>
       <c r="B45" s="42">
         <v>42</v>
       </c>
@@ -2824,7 +2827,7 @@
       <c r="H45" s="8"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="92"/>
+      <c r="A46" s="84"/>
       <c r="B46" s="42">
         <v>43</v>
       </c>
@@ -2844,7 +2847,7 @@
       <c r="H46" s="8"/>
     </row>
     <row r="47" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="95" t="s">
+      <c r="A47" s="87" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="43">
@@ -2866,7 +2869,7 @@
       </c>
     </row>
     <row r="48" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="95"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="43">
         <v>45</v>
       </c>
@@ -2884,7 +2887,7 @@
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="A49" s="95"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="43">
         <v>46</v>
       </c>
@@ -2904,7 +2907,7 @@
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="95"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="43">
         <v>47</v>
       </c>
@@ -2922,7 +2925,7 @@
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="95"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="43">
         <v>48</v>
       </c>
@@ -2939,7 +2942,7 @@
       <c r="G51" s="78"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="91" t="s">
+      <c r="A52" s="83" t="s">
         <v>65</v>
       </c>
       <c r="B52" s="41">
@@ -2961,7 +2964,7 @@
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="91"/>
+      <c r="A53" s="83"/>
       <c r="B53" s="41">
         <v>50</v>
       </c>
@@ -2980,7 +2983,7 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="91"/>
+      <c r="A54" s="83"/>
       <c r="B54" s="41">
         <v>51</v>
       </c>
@@ -2998,7 +3001,7 @@
       <c r="H54" s="8"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="91"/>
+      <c r="A55" s="83"/>
       <c r="B55" s="41">
         <v>52</v>
       </c>
@@ -3018,7 +3021,7 @@
       <c r="H55" s="8"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="91"/>
+      <c r="A56" s="83"/>
       <c r="B56" s="41">
         <v>53</v>
       </c>
@@ -3036,7 +3039,7 @@
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="91"/>
+      <c r="A57" s="83"/>
       <c r="B57" s="41">
         <v>54</v>
       </c>
@@ -3056,7 +3059,7 @@
       <c r="H57" s="8"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="91"/>
+      <c r="A58" s="83"/>
       <c r="B58" s="41">
         <v>55</v>
       </c>
@@ -3074,7 +3077,7 @@
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="91"/>
+      <c r="A59" s="83"/>
       <c r="B59" s="41">
         <v>56</v>
       </c>
@@ -3092,7 +3095,7 @@
       <c r="H59" s="8"/>
     </row>
     <row r="60" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="91"/>
+      <c r="A60" s="83"/>
       <c r="B60" s="41">
         <v>57</v>
       </c>
@@ -3104,13 +3107,15 @@
         <v>10</v>
       </c>
       <c r="F60" s="61" t="s">
-        <v>11</v>
-      </c>
-      <c r="G60" s="75"/>
+        <v>222</v>
+      </c>
+      <c r="G60" s="75" t="s">
+        <v>274</v>
+      </c>
       <c r="H60" s="8"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="91"/>
+      <c r="A61" s="83"/>
       <c r="B61" s="41">
         <v>58</v>
       </c>
@@ -3122,13 +3127,13 @@
         <v>10</v>
       </c>
       <c r="F61" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G61" s="75"/>
       <c r="H61" s="8"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="91"/>
+      <c r="A62" s="83"/>
       <c r="B62" s="41">
         <v>59</v>
       </c>
@@ -3146,7 +3151,7 @@
       <c r="H62" s="8"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="92" t="s">
+      <c r="A63" s="84" t="s">
         <v>78</v>
       </c>
       <c r="B63" s="42">
@@ -3166,7 +3171,7 @@
       <c r="H63" s="8"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="92"/>
+      <c r="A64" s="84"/>
       <c r="B64" s="42">
         <v>61</v>
       </c>
@@ -3186,7 +3191,7 @@
       <c r="H64" s="8"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="92"/>
+      <c r="A65" s="84"/>
       <c r="B65" s="42">
         <v>62</v>
       </c>
@@ -3204,7 +3209,7 @@
       <c r="H65" s="8"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="92"/>
+      <c r="A66" s="84"/>
       <c r="B66" s="42">
         <v>63</v>
       </c>
@@ -3222,7 +3227,7 @@
       <c r="H66" s="8"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="92"/>
+      <c r="A67" s="84"/>
       <c r="B67" s="42">
         <v>64</v>
       </c>
@@ -3242,7 +3247,7 @@
       <c r="H67" s="8"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="92"/>
+      <c r="A68" s="84"/>
       <c r="B68" s="42">
         <v>65</v>
       </c>
@@ -3254,13 +3259,13 @@
         <v>10</v>
       </c>
       <c r="F68" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G68" s="75"/>
       <c r="H68" s="8"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="92"/>
+      <c r="A69" s="84"/>
       <c r="B69" s="42">
         <v>66</v>
       </c>
@@ -3278,7 +3283,7 @@
       <c r="H69" s="8"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="92"/>
+      <c r="A70" s="84"/>
       <c r="B70" s="42">
         <v>67</v>
       </c>
@@ -3290,13 +3295,13 @@
         <v>10</v>
       </c>
       <c r="F70" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G70" s="75"/>
       <c r="H70" s="8"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="92"/>
+      <c r="A71" s="84"/>
       <c r="B71" s="42">
         <v>68</v>
       </c>
@@ -3308,14 +3313,14 @@
         <v>10</v>
       </c>
       <c r="F71" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G71" s="76" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="92"/>
+      <c r="A72" s="84"/>
       <c r="B72" s="42">
         <v>69</v>
       </c>
@@ -3333,7 +3338,7 @@
       <c r="H72" s="8"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="92"/>
+      <c r="A73" s="84"/>
       <c r="B73" s="42">
         <v>70</v>
       </c>
@@ -3351,7 +3356,7 @@
       <c r="H73" s="8"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="92"/>
+      <c r="A74" s="84"/>
       <c r="B74" s="42">
         <v>71</v>
       </c>
@@ -3369,7 +3374,7 @@
       <c r="H74" s="8"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="92"/>
+      <c r="A75" s="84"/>
       <c r="B75" s="42">
         <v>72</v>
       </c>
@@ -3387,7 +3392,7 @@
       <c r="H75" s="8"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="92"/>
+      <c r="A76" s="84"/>
       <c r="B76" s="42">
         <v>73</v>
       </c>
@@ -3405,7 +3410,7 @@
       <c r="H76" s="8"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="92"/>
+      <c r="A77" s="84"/>
       <c r="B77" s="42">
         <v>74</v>
       </c>
@@ -3423,7 +3428,7 @@
       <c r="H77" s="8"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="92"/>
+      <c r="A78" s="84"/>
       <c r="B78" s="42">
         <v>75</v>
       </c>
@@ -3443,7 +3448,7 @@
       <c r="H78" s="8"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="90" t="s">
+      <c r="A79" s="82" t="s">
         <v>96</v>
       </c>
       <c r="B79" s="43">
@@ -3463,7 +3468,7 @@
       <c r="H79" s="8"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="90"/>
+      <c r="A80" s="82"/>
       <c r="B80" s="43">
         <v>77</v>
       </c>
@@ -3481,7 +3486,7 @@
       <c r="H80" s="8"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="90"/>
+      <c r="A81" s="82"/>
       <c r="B81" s="43">
         <v>78</v>
       </c>
@@ -3500,7 +3505,7 @@
       <c r="G81" s="79"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="90"/>
+      <c r="A82" s="82"/>
       <c r="B82" s="43">
         <v>79</v>
       </c>
@@ -3517,7 +3522,7 @@
       <c r="G82" s="79"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="90"/>
+      <c r="A83" s="82"/>
       <c r="B83" s="43">
         <v>80</v>
       </c>
@@ -3529,7 +3534,7 @@
         <v>10</v>
       </c>
       <c r="F83" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G83" s="76" t="s">
         <v>273</v>
@@ -3668,144 +3673,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="90" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
-      <c r="S1" s="97"/>
-      <c r="T1" s="97"/>
-      <c r="U1" s="97"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
-      <c r="J2" s="97"/>
-      <c r="K2" s="97"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
-      <c r="N2" s="97"/>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="97"/>
-      <c r="U2" s="97"/>
+      <c r="A2" s="91"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
-      <c r="J3" s="97"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-      <c r="T3" s="97"/>
-      <c r="U3" s="97"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="91"/>
+      <c r="I3" s="91"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="91"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="91"/>
+      <c r="S3" s="91"/>
+      <c r="T3" s="91"/>
+      <c r="U3" s="91"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="97"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="91"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="91"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="91"/>
+      <c r="M4" s="91"/>
+      <c r="N4" s="91"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="91"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="91"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="91"/>
+      <c r="U4" s="91"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
-      <c r="I5" s="97"/>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="97"/>
-      <c r="N5" s="97"/>
-      <c r="O5" s="97"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="97"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="97"/>
-      <c r="U5" s="97"/>
+      <c r="A5" s="91"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="91"/>
+      <c r="P5" s="91"/>
+      <c r="Q5" s="91"/>
+      <c r="R5" s="91"/>
+      <c r="S5" s="91"/>
+      <c r="T5" s="91"/>
+      <c r="U5" s="91"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="97"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="97"/>
-      <c r="M6" s="97"/>
-      <c r="N6" s="97"/>
-      <c r="O6" s="97"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="97"/>
-      <c r="R6" s="97"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="97"/>
-      <c r="U6" s="97"/>
+      <c r="A6" s="91"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -3844,26 +3849,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
     </row>
     <row r="2" spans="1:7" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="96" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="86"/>
-      <c r="C2" s="86"/>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="86"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="35"/>
@@ -3881,7 +3886,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="93" t="s">
         <v>106</v>
       </c>
       <c r="B4" s="62">
@@ -3902,7 +3907,7 @@
       <c r="G4" s="20"/>
     </row>
     <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="83"/>
+      <c r="A5" s="93"/>
       <c r="B5" s="62">
         <v>2</v>
       </c>
@@ -3919,7 +3924,7 @@
       <c r="G5" s="23"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="62">
         <v>3</v>
       </c>
@@ -3936,7 +3941,7 @@
       <c r="G6" s="23"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
+      <c r="A7" s="93"/>
       <c r="B7" s="62">
         <v>4</v>
       </c>
@@ -3953,7 +3958,7 @@
       <c r="G7" s="23"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
+      <c r="A8" s="93"/>
       <c r="B8" s="62">
         <v>5</v>
       </c>
@@ -3970,7 +3975,7 @@
       <c r="G8" s="23"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="62">
         <v>6</v>
       </c>
@@ -3987,7 +3992,7 @@
       <c r="G9" s="23"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="83"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="62">
         <v>7</v>
       </c>
@@ -4004,7 +4009,7 @@
       <c r="G10" s="23"/>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="97" t="s">
         <v>115</v>
       </c>
       <c r="B11" s="66">
@@ -4023,7 +4028,7 @@
       <c r="G11" s="23"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="87"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="66">
         <v>9</v>
       </c>
@@ -4040,7 +4045,7 @@
       <c r="G12" s="23"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="87"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="66">
         <v>10</v>
       </c>
@@ -4052,12 +4057,12 @@
         <v>10</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G13" s="23"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="87"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="66">
         <v>11</v>
       </c>
@@ -4074,7 +4079,7 @@
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="87"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="66">
         <v>12</v>
       </c>
@@ -4091,7 +4096,7 @@
       <c r="G15" s="23"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="87"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="66">
         <v>13</v>
       </c>
@@ -4108,7 +4113,7 @@
       <c r="G16" s="23"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="87"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="66">
         <v>14</v>
       </c>
@@ -4125,7 +4130,7 @@
       <c r="G17" s="23"/>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="87"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="66">
         <v>15</v>
       </c>
@@ -4144,7 +4149,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="87"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="66">
         <v>16</v>
       </c>
@@ -4161,7 +4166,7 @@
       <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="87"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="66">
         <v>17</v>
       </c>
@@ -4178,7 +4183,7 @@
       <c r="G20" s="23"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="87"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="66">
         <v>18</v>
       </c>
@@ -4195,7 +4200,7 @@
       <c r="G21" s="23"/>
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="94" t="s">
         <v>128</v>
       </c>
       <c r="B22" s="72">
@@ -4214,7 +4219,7 @@
       <c r="G22" s="23"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="84"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="72">
         <v>20</v>
       </c>
@@ -4226,12 +4231,12 @@
         <v>10</v>
       </c>
       <c r="F23" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G23" s="23"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="84"/>
+      <c r="A24" s="94"/>
       <c r="B24" s="72">
         <v>21</v>
       </c>
@@ -4248,7 +4253,7 @@
       <c r="G24" s="23"/>
     </row>
     <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="84"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="72">
         <v>22</v>
       </c>
@@ -4265,7 +4270,7 @@
       <c r="G25" s="23"/>
     </row>
     <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="84"/>
+      <c r="A26" s="94"/>
       <c r="B26" s="72">
         <v>23</v>
       </c>
@@ -4277,12 +4282,12 @@
         <v>10</v>
       </c>
       <c r="F26" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G26" s="23"/>
     </row>
     <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="84"/>
+      <c r="A27" s="94"/>
       <c r="B27" s="72">
         <v>24</v>
       </c>
@@ -4294,12 +4299,12 @@
         <v>109</v>
       </c>
       <c r="F27" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G27" s="23"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="84"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="72">
         <v>25</v>
       </c>
@@ -4316,7 +4321,7 @@
       <c r="G28" s="23"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="84"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="72">
         <v>26</v>
       </c>
@@ -4328,12 +4333,12 @@
         <v>10</v>
       </c>
       <c r="F29" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G29" s="23"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
+      <c r="A30" s="93" t="s">
         <v>137</v>
       </c>
       <c r="B30" s="62">
@@ -4347,12 +4352,12 @@
         <v>10</v>
       </c>
       <c r="F30" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G30" s="23"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="83"/>
+      <c r="A31" s="93"/>
       <c r="B31" s="62">
         <v>28</v>
       </c>
@@ -4364,12 +4369,12 @@
         <v>10</v>
       </c>
       <c r="F31" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G31" s="23"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="83"/>
+      <c r="A32" s="93"/>
       <c r="B32" s="62">
         <v>29</v>
       </c>
@@ -4381,12 +4386,12 @@
         <v>10</v>
       </c>
       <c r="F32" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G32" s="23"/>
     </row>
     <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="83"/>
+      <c r="A33" s="93"/>
       <c r="B33" s="62">
         <v>30</v>
       </c>
@@ -4403,7 +4408,7 @@
       <c r="G33" s="23"/>
     </row>
     <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="83"/>
+      <c r="A34" s="93"/>
       <c r="B34" s="62">
         <v>31</v>
       </c>
@@ -4415,12 +4420,12 @@
         <v>10</v>
       </c>
       <c r="F34" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G34" s="23"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="83"/>
+      <c r="A35" s="93"/>
       <c r="B35" s="62">
         <v>32</v>
       </c>
@@ -4432,12 +4437,12 @@
         <v>10</v>
       </c>
       <c r="F35" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G35" s="23"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="83"/>
+      <c r="A36" s="93"/>
       <c r="B36" s="62">
         <v>33</v>
       </c>
@@ -4454,7 +4459,7 @@
       <c r="G36" s="23"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="83"/>
+      <c r="A37" s="93"/>
       <c r="B37" s="62">
         <v>34</v>
       </c>
@@ -4471,7 +4476,7 @@
       <c r="G37" s="23"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="83"/>
+      <c r="A38" s="93"/>
       <c r="B38" s="62">
         <v>35</v>
       </c>
@@ -4488,7 +4493,7 @@
       <c r="G38" s="23"/>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="83"/>
+      <c r="A39" s="93"/>
       <c r="B39" s="62">
         <v>36</v>
       </c>
@@ -4505,7 +4510,7 @@
       <c r="G39" s="23"/>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="83"/>
+      <c r="A40" s="93"/>
       <c r="B40" s="62">
         <v>37</v>
       </c>
@@ -4522,7 +4527,7 @@
       <c r="G40" s="23"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="83"/>
+      <c r="A41" s="93"/>
       <c r="B41" s="62">
         <v>38</v>
       </c>
@@ -4539,7 +4544,7 @@
       <c r="G41" s="23"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="83"/>
+      <c r="A42" s="93"/>
       <c r="B42" s="62">
         <v>39</v>
       </c>
@@ -4556,7 +4561,7 @@
       <c r="G42" s="23"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="83"/>
+      <c r="A43" s="93"/>
       <c r="B43" s="62">
         <v>40</v>
       </c>
@@ -4573,7 +4578,7 @@
       <c r="G43" s="23"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="83"/>
+      <c r="A44" s="93"/>
       <c r="B44" s="62">
         <v>41</v>
       </c>
@@ -4590,7 +4595,7 @@
       <c r="G44" s="23"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="83"/>
+      <c r="A45" s="93"/>
       <c r="B45" s="62">
         <v>42</v>
       </c>
@@ -4607,7 +4612,7 @@
       <c r="G45" s="23"/>
     </row>
     <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="83"/>
+      <c r="A46" s="93"/>
       <c r="B46" s="62">
         <v>43</v>
       </c>
@@ -4619,12 +4624,12 @@
         <v>10</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>11</v>
+        <v>224</v>
       </c>
       <c r="G46" s="23"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="87" t="s">
+      <c r="A47" s="97" t="s">
         <v>157</v>
       </c>
       <c r="B47" s="66">
@@ -4643,7 +4648,7 @@
       <c r="G47" s="23"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="87"/>
+      <c r="A48" s="97"/>
       <c r="B48" s="66">
         <v>45</v>
       </c>
@@ -4655,12 +4660,12 @@
         <v>10</v>
       </c>
       <c r="F48" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G48" s="23"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="87"/>
+      <c r="A49" s="97"/>
       <c r="B49" s="66">
         <v>46</v>
       </c>
@@ -4677,7 +4682,7 @@
       <c r="G49" s="23"/>
     </row>
     <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="87"/>
+      <c r="A50" s="97"/>
       <c r="B50" s="66">
         <v>47</v>
       </c>
@@ -4694,7 +4699,7 @@
       <c r="G50" s="23"/>
     </row>
     <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="87"/>
+      <c r="A51" s="97"/>
       <c r="B51" s="66">
         <v>48</v>
       </c>
@@ -4711,7 +4716,7 @@
       <c r="G51" s="23"/>
     </row>
     <row r="52" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="87"/>
+      <c r="A52" s="97"/>
       <c r="B52" s="66">
         <v>49</v>
       </c>
@@ -4728,7 +4733,7 @@
       <c r="G52" s="23"/>
     </row>
     <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="87"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="66">
         <v>50</v>
       </c>
@@ -4745,7 +4750,7 @@
       <c r="G53" s="23"/>
     </row>
     <row r="54" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="87"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="66">
         <v>51</v>
       </c>
@@ -4762,7 +4767,7 @@
       <c r="G54" s="23"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="87"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="66">
         <v>52</v>
       </c>
@@ -4779,7 +4784,7 @@
       <c r="G55" s="23"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="87"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="66">
         <v>53</v>
       </c>
@@ -4796,7 +4801,7 @@
       <c r="G56" s="23"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="87"/>
+      <c r="A57" s="97"/>
       <c r="B57" s="66">
         <v>54</v>
       </c>
@@ -4813,7 +4818,7 @@
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="87"/>
+      <c r="A58" s="97"/>
       <c r="B58" s="66">
         <v>55</v>
       </c>
@@ -4825,12 +4830,12 @@
         <v>10</v>
       </c>
       <c r="F58" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G58" s="23"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="87"/>
+      <c r="A59" s="97"/>
       <c r="B59" s="66">
         <v>56</v>
       </c>
@@ -4847,7 +4852,7 @@
       <c r="G59" s="23"/>
     </row>
     <row r="60" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A60" s="87"/>
+      <c r="A60" s="97"/>
       <c r="B60" s="66">
         <v>57</v>
       </c>
@@ -4859,12 +4864,12 @@
         <v>10</v>
       </c>
       <c r="F60" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G60" s="23"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="87"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="66">
         <v>58</v>
       </c>
@@ -4881,7 +4886,7 @@
       <c r="G61" s="23"/>
     </row>
     <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="87"/>
+      <c r="A62" s="97"/>
       <c r="B62" s="66">
         <v>59</v>
       </c>
@@ -4898,7 +4903,7 @@
       <c r="G62" s="23"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="87"/>
+      <c r="A63" s="97"/>
       <c r="B63" s="66">
         <v>60</v>
       </c>
@@ -4915,7 +4920,7 @@
       <c r="G63" s="23"/>
     </row>
     <row r="64" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="87"/>
+      <c r="A64" s="97"/>
       <c r="B64" s="66">
         <v>61</v>
       </c>
@@ -4932,7 +4937,7 @@
       <c r="G64" s="23"/>
     </row>
     <row r="65" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="87"/>
+      <c r="A65" s="97"/>
       <c r="B65" s="66">
         <v>62</v>
       </c>
@@ -4949,7 +4954,7 @@
       <c r="G65" s="23"/>
     </row>
     <row r="66" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A66" s="87"/>
+      <c r="A66" s="97"/>
       <c r="B66" s="66">
         <v>63</v>
       </c>
@@ -4961,12 +4966,12 @@
         <v>184</v>
       </c>
       <c r="F66" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="G66" s="23"/>
     </row>
     <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="87"/>
+      <c r="A67" s="97"/>
       <c r="B67" s="66">
         <v>64</v>
       </c>
@@ -4983,7 +4988,7 @@
       <c r="G67" s="23"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="87"/>
+      <c r="A68" s="97"/>
       <c r="B68" s="66">
         <v>65</v>
       </c>
@@ -5000,7 +5005,7 @@
       <c r="G68" s="23"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="87"/>
+      <c r="A69" s="97"/>
       <c r="B69" s="66">
         <v>66</v>
       </c>
@@ -5017,7 +5022,7 @@
       <c r="G69" s="23"/>
     </row>
     <row r="70" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A70" s="87"/>
+      <c r="A70" s="97"/>
       <c r="B70" s="66">
         <v>67</v>
       </c>
@@ -5029,12 +5034,12 @@
         <v>10</v>
       </c>
       <c r="F70" s="61" t="s">
-        <v>11</v>
+        <v>222</v>
       </c>
       <c r="G70" s="23"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="84" t="s">
+      <c r="A71" s="94" t="s">
         <v>189</v>
       </c>
       <c r="B71" s="72">
@@ -5053,7 +5058,7 @@
       <c r="G71" s="23"/>
     </row>
     <row r="72" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A72" s="84"/>
+      <c r="A72" s="94"/>
       <c r="B72" s="72">
         <v>69</v>
       </c>
@@ -5070,7 +5075,7 @@
       <c r="G72" s="23"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="84"/>
+      <c r="A73" s="94"/>
       <c r="B73" s="72">
         <v>70</v>
       </c>
@@ -5087,7 +5092,7 @@
       <c r="G73" s="23"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="84"/>
+      <c r="A74" s="94"/>
       <c r="B74" s="72">
         <v>71</v>
       </c>
@@ -5104,7 +5109,7 @@
       <c r="G74" s="23"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="84"/>
+      <c r="A75" s="94"/>
       <c r="B75" s="72">
         <v>72</v>
       </c>
@@ -5121,7 +5126,7 @@
       <c r="G75" s="23"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="82" t="s">
+      <c r="A76" s="92" t="s">
         <v>196</v>
       </c>
       <c r="B76" s="62">
@@ -5140,7 +5145,7 @@
       <c r="G76" s="23"/>
     </row>
     <row r="77" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="83"/>
+      <c r="A77" s="93"/>
       <c r="B77" s="62">
         <v>74</v>
       </c>
@@ -5313,7 +5318,7 @@
         <v>200</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="D4" s="23"/>
     </row>
@@ -5325,7 +5330,7 @@
         <v>201</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>11</v>
+        <v>223</v>
       </c>
       <c r="D5" s="23"/>
     </row>
